--- a/estadistica2/data/paz_ayala.xlsx
+++ b/estadistica2/data/paz_ayala.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7015BBE-6EB5-1E40-997A-7FA9ED043F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F562B60-4C79-C548-93E4-805AB7A4E54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="780" windowWidth="27640" windowHeight="15780" xr2:uid="{9038EB51-BBAE-3E43-B2F6-C58DCDA3F4FD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="codebook" sheetId="2" r:id="rId2"/>
+    <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">codebook!$A$1:$D$1</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="33">
   <si>
     <t>country</t>
   </si>
@@ -126,14 +127,29 @@
   <si>
     <t>exchange_rate</t>
   </si>
+  <si>
+    <t>VD</t>
+  </si>
+  <si>
+    <t>VI1</t>
+  </si>
+  <si>
+    <t>VI2</t>
+  </si>
+  <si>
+    <t>VI3</t>
+  </si>
+  <si>
+    <t>VI4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000000000000000000000000000"/>
-    <numFmt numFmtId="166" formatCode="0.00000000000000000000000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000000000000000000000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000000000000000000000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -214,20 +230,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18397,4 +18413,39 @@
   <autoFilter ref="A1:D1" xr:uid="{518C0B78-E702-1645-9E07-0293744BDA82}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FD917B-58E2-384F-9474-982E43DE1E4B}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/estadistica2/data/paz_ayala.xlsx
+++ b/estadistica2/data/paz_ayala.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F562B60-4C79-C548-93E4-805AB7A4E54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DA32E7B-886C-9341-8F56-64D4BFE118A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="780" windowWidth="27640" windowHeight="15780" xr2:uid="{9038EB51-BBAE-3E43-B2F6-C58DCDA3F4FD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{9038EB51-BBAE-3E43-B2F6-C58DCDA3F4FD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">codebook!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="38">
   <si>
     <t>country</t>
   </si>
@@ -101,18 +101,6 @@
     <t>nivel de precios del consumo de los hogares</t>
   </si>
   <si>
-    <t>Nivel de precios de CCON (PPP/XR), nivel de precios del PIBo de USA en 2017=1</t>
-  </si>
-  <si>
-    <t>Nivel de precios de CDA (PPP/XR), nivel de precios del PIBo de USA en 2017=1</t>
-  </si>
-  <si>
-    <t>Nivel de precios de CGDPo (PPP/XR), nivel de precios del PIBo de USA en 2017=1</t>
-  </si>
-  <si>
-    <t>Tipo de cambio, moneda nacional/USD (mercado+estimado)</t>
-  </si>
-  <si>
     <t>general_consumption_price</t>
   </si>
   <si>
@@ -142,6 +130,33 @@
   <si>
     <t>VI4</t>
   </si>
+  <si>
+    <t>paises de muestra</t>
+  </si>
+  <si>
+    <t>costo del consumo de los hogares entre países, ajustado por poder adquisitivo.</t>
+  </si>
+  <si>
+    <t>compara costo de los bienes y servicios internos entre países y a lo largo del tiempo.</t>
+  </si>
+  <si>
+    <t>costo relativo de todos los bienes y servicios producidos en una economía.</t>
+  </si>
+  <si>
+    <t>argentina</t>
+  </si>
+  <si>
+    <t>venezuela</t>
+  </si>
+  <si>
+    <t>VI5</t>
+  </si>
+  <si>
+    <t>VI6</t>
+  </si>
+  <si>
+    <t>unidad de moneda local equivalente a un 1 dólar.</t>
+  </si>
 </sst>
 </file>
 
@@ -151,7 +166,7 @@
     <numFmt numFmtId="164" formatCode="0.000000000000000000000000000"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000000000000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -185,40 +200,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -243,7 +245,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,12 +581,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4719DC20-A7B1-7E46-9C87-5598A1E94F83}">
   <dimension ref="A1:G771"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -598,19 +600,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -18287,12 +18289,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518C0B78-E702-1645-9E07-0293744BDA82}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="25.5" customWidth="1"/>
+    <col min="2" max="2" width="66.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -18314,9 +18316,15 @@
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -18336,7 +18344,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>18</v>
@@ -18351,10 +18359,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5">
         <v>5.1255226135253906E-2</v>
@@ -18366,10 +18374,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5">
         <v>5.1714338362216949E-2</v>
@@ -18381,10 +18389,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C7" s="5">
         <v>5.2024088799953461E-2</v>
@@ -18396,10 +18404,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C8" s="9">
         <v>7.8940727933892703E-15</v>
@@ -18412,40 +18420,76 @@
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{518C0B78-E702-1645-9E07-0293744BDA82}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FD917B-58E2-384F-9474-982E43DE1E4B}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>32</v>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>